--- a/assessment_forms/023_data_compression_knowledge_quiz--assessment_forms.xlsx
+++ b/assessment_forms/023_data_compression_knowledge_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lossless_field</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lossless Field</t>
+          <t>What is the primary goal of lossless data compression?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lossy_field</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lossy Field</t>
+          <t>What is the difference between lossless and lossy compression?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>How does lossless compression impact data integrity?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the benefits of lossless data compression?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>How does lossy compression impact data quality?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the applications of lossless data compression?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the trade-offs between lossless and lossy compression?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>How does lossless compression handle errors?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the types of data that can be compressed using lossless methods?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Can lossless compression be used for real-time data transmission?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>How does lossy compression impact data compression ratio?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the limitations of lossless data compression?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,20 +801,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the differences between various lossless compression algorithms?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,13 +824,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Can lossy compression be used for image and video compression?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,20 +847,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>How does lossless compression handle compression artifacts?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the benefits of lossy compression?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,20 +893,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Can lossless compression be used for audio compression?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,174 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>What are the types of data that can be compressed using lossy methods?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,612 +965,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lossless_field_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless_compression</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Lossless Compression</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lossless_field_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>lossy_compression</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Lossy Compression</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lossy_field_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lossy_field_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>loss_in_quality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Loss in Quality</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>no_loss_in_quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>No Loss in Quality</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless_data_compression</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Lossless Data Compression</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>lossy_data_compression</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Lossy Data Compression</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>error-free</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Error-Free</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>error-prone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Error-Prone</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>image_data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Image Data</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>video_data</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Video Data</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>audio_data</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Audio Data</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>text_data</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Text Data</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>better_ratio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Better Ratio</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>worse_ratio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Worse Ratio</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>algorithm_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Algorithm 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>algorithm_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Algorithm 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>algorithm_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Algorithm 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>no_artifacts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>No Artifacts</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>some_artifacts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Some Artifacts</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>image_data</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lossless</t>
+          <t>Image Data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lossy</t>
+          <t>audio_data</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lossy</t>
+          <t>Audio Data</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>video_data</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lossless</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>lossy</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>lossless</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Lossless</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>lossy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>lossless</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Lossless</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>lossy</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Lossy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>lossless</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Lossless</t>
+          <t>Video Data</t>
         </is>
       </c>
     </row>
